--- a/011.Copy Formula.xlsx
+++ b/011.Copy Formula.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD7718A-FB90-48D2-A899-8A2CF1E08840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B11EB08-DB55-4D45-B7DE-8FDC762BFC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>January</t>
   </si>
@@ -92,16 +92,24 @@
   </si>
   <si>
     <t>Books and Beyond - Mideastern Region</t>
+  </si>
+  <si>
+    <t>Newberry</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,11 +132,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,10 +520,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P31"/>
+  <dimension ref="B2:P32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
     <col min="11" max="11" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -636,285 +646,306 @@
         <v>850</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+    <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>150</v>
+      </c>
+      <c r="D10">
+        <v>200</v>
+      </c>
+      <c r="E10">
+        <v>185</v>
+      </c>
+      <c r="F10">
+        <v>225</v>
+      </c>
+      <c r="G10">
+        <f>SUM(C10:F10)</f>
+        <v>760</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="C11">
-        <f>SUM(C6:C9)</f>
-        <v>740</v>
-      </c>
-      <c r="D11">
-        <f t="shared" ref="D11:G11" si="0">SUM(D6:D9)</f>
-        <v>765</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>760</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
+      <c r="C12">
+        <f>SUM(C6:C10)</f>
+        <v>890</v>
+      </c>
+      <c r="D12">
+        <f>SUM(D6:D10)</f>
+        <v>965</v>
+      </c>
+      <c r="E12">
+        <f>SUM(E6:E10)</f>
+        <v>945</v>
+      </c>
+      <c r="F12">
+        <f>SUM(F6:F10)</f>
+        <v>1125</v>
+      </c>
+      <c r="G12">
+        <f>SUM(G6:G10)</f>
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <f>AVERAGE(C6:C10)</f>
+        <v>178</v>
+      </c>
+      <c r="D14">
+        <f>AVERAGE(D6:D10)</f>
+        <v>193</v>
+      </c>
+      <c r="E14">
+        <f>AVERAGE(E6:E10)</f>
+        <v>189</v>
+      </c>
+      <c r="F14">
+        <f>AVERAGE(F6:F10)</f>
+        <v>225</v>
+      </c>
+      <c r="G14">
+        <f>AVERAGE(G6:G10)</f>
+        <v>785</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <f>MAX(C6:C10)</f>
+        <v>220</v>
+      </c>
+      <c r="D16">
+        <f>MAX(D6:D10)</f>
+        <v>210</v>
+      </c>
+      <c r="E16">
+        <f>MAX(E6:E10)</f>
+        <v>240</v>
+      </c>
+      <c r="F16">
+        <f>MAX(F6:F10)</f>
+        <v>310</v>
+      </c>
+      <c r="G16">
+        <f>MAX(G6:G10)</f>
         <v>900</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>3165</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13">
-        <f>AVERAGE(C6:C9)</f>
-        <v>185</v>
-      </c>
-      <c r="D13">
-        <f t="shared" ref="D13:G13" si="1">AVERAGE(D6:D9)</f>
-        <v>191.25</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="1"/>
-        <v>190</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="1"/>
-        <v>225</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="1"/>
-        <v>791.25</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <f>MAX(C6:C9)</f>
-        <v>220</v>
-      </c>
-      <c r="D15">
-        <f t="shared" ref="D15:G15" si="2">MAX(D6:D9)</f>
-        <v>210</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="2"/>
-        <v>240</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="2"/>
-        <v>310</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="2"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C19" s="1" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C20" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21">
-        <v>250</v>
-      </c>
-      <c r="D21">
-        <v>385</v>
-      </c>
-      <c r="E21">
-        <v>755</v>
-      </c>
-      <c r="F21">
-        <v>550</v>
-      </c>
-      <c r="G21">
-        <f>SUM(C21:F21)</f>
-        <v>1940</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="D22">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="E22">
-        <v>230</v>
+        <v>755</v>
       </c>
       <c r="F22">
-        <v>475</v>
+        <v>550</v>
       </c>
       <c r="G22">
         <f>SUM(C22:F22)</f>
-        <v>1495</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="D23">
-        <v>170</v>
+        <v>410</v>
       </c>
       <c r="E23">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="F23">
-        <v>350</v>
+        <v>475</v>
       </c>
       <c r="G23">
         <f>SUM(C23:F23)</f>
-        <v>955</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>460</v>
+        <v>110</v>
       </c>
       <c r="D24">
-        <v>525</v>
+        <v>170</v>
       </c>
       <c r="E24">
-        <v>580</v>
+        <v>325</v>
       </c>
       <c r="F24">
-        <v>685</v>
+        <v>350</v>
       </c>
       <c r="G24">
         <f>SUM(C24:F24)</f>
-        <v>2250</v>
+        <v>955</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="D25">
-        <v>335</v>
+        <v>525</v>
       </c>
       <c r="E25">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="F25">
-        <v>610</v>
+        <v>685</v>
       </c>
       <c r="G25">
         <f>SUM(C25:F25)</f>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>500</v>
+      </c>
+      <c r="D26">
+        <v>335</v>
+      </c>
+      <c r="E26">
+        <v>450</v>
+      </c>
+      <c r="F26">
+        <v>610</v>
+      </c>
+      <c r="G26">
+        <f>SUM(C26:F26)</f>
         <v>1895</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="C27">
-        <f>SUM(C21:C25)</f>
+      <c r="C28">
+        <f>SUM(C22:C26)</f>
         <v>1700</v>
       </c>
-      <c r="D27">
-        <f t="shared" ref="D27:G27" si="3">SUM(D21:D25)</f>
+      <c r="D28">
+        <f>SUM(D22:D26)</f>
         <v>1825</v>
       </c>
-      <c r="E27">
-        <f t="shared" si="3"/>
+      <c r="E28">
+        <f>SUM(E22:E26)</f>
         <v>2340</v>
       </c>
-      <c r="F27">
-        <f t="shared" si="3"/>
+      <c r="F28">
+        <f>SUM(F22:F26)</f>
         <v>2670</v>
       </c>
-      <c r="G27">
-        <f t="shared" si="3"/>
+      <c r="G28">
+        <f>SUM(G22:G26)</f>
         <v>8535</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
         <v>15</v>
       </c>
-      <c r="C29">
-        <f>AVERAGE(C21:C25)</f>
+      <c r="C30">
+        <f>AVERAGE(C22:C26)</f>
         <v>340</v>
       </c>
-      <c r="D29">
-        <f t="shared" ref="D29:G29" si="4">AVERAGE(D21:D25)</f>
+      <c r="D30">
+        <f>AVERAGE(D22:D26)</f>
         <v>365</v>
       </c>
-      <c r="E29">
-        <f t="shared" si="4"/>
+      <c r="E30">
+        <f>AVERAGE(E22:E26)</f>
         <v>468</v>
       </c>
-      <c r="F29">
-        <f t="shared" si="4"/>
+      <c r="F30">
+        <f>AVERAGE(F22:F26)</f>
         <v>534</v>
       </c>
-      <c r="G29">
-        <f t="shared" si="4"/>
+      <c r="G30">
+        <f>AVERAGE(G22:G26)</f>
         <v>1707</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
         <v>16</v>
       </c>
-      <c r="C31">
-        <f>MAX(C21:C25)</f>
+      <c r="C32">
+        <f>MAX(C22:C26)</f>
         <v>500</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:G31" si="5">MAX(D21:D25)</f>
+      <c r="D32">
+        <f>MAX(D22:D26)</f>
         <v>525</v>
       </c>
-      <c r="E31">
-        <f t="shared" si="5"/>
+      <c r="E32">
+        <f>MAX(E22:E26)</f>
         <v>755</v>
       </c>
-      <c r="F31">
-        <f t="shared" si="5"/>
+      <c r="F32">
+        <f>MAX(F22:F26)</f>
         <v>685</v>
       </c>
-      <c r="G31">
-        <f t="shared" si="5"/>
+      <c r="G32">
+        <f>MAX(G22:G26)</f>
         <v>2250</v>
       </c>
     </row>
